--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,7 +713,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>ng6idLW1</t>
+          <t>8KIT2SzJ</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -721,42 +721,380 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">villanueva j  i 
+          <t xml:space="preserve">ortiz m 
   esp </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0Q3vjDhH</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>bs5KnIiT</t>
+          <t>b3KjrVYq</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
+          <t>QekfJmLa</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lopez m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AD5WKzFn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>vJDNK0d4</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">garcia v 
+  esp </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>p2dFnNso</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>WhAFMMRi</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AD5WKzFn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>OQqSjnv9</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>YcAFQVSP</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>IVonL9jm</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrera r 
+  esp </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>hA5zaJZp</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maeso f 
+  esp </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>MNr3HRkC</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diaz de mera i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>ChPK4l66</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ruiz a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>A7v4ruhp</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>hpMqQeYq</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ortiz m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>4KmdZaBc</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villanueva j  i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>bs5KnIiT</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>8CpDVHAM</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villanueva j  i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>bs5KnIiT</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>ng6idLW1</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villanueva j  i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>bs5KnIiT</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
           <t>CWcwKOO8</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t xml:space="preserve">garcia v 
   esp </t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>nZQG5IgJ</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>p2dFnNso</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -765,7 +765,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>ng6idLW1</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -773,25 +773,25 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">garcia v 
+          <t xml:space="preserve">villanueva j  i 
   esp </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>0Q3vjDhH</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>p2dFnNso</t>
+          <t>bs5KnIiT</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
+          <t>CWcwKOO8</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -799,302 +799,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera montero j 
+          <t xml:space="preserve">garcia v 
   esp </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>AD5WKzFn</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>EJmuzs93</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>OQqSjnv9</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sanchez j 
-  esp </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>UsfeP2jC</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>AZ18LjKN</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>YcAFQVSP</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">munuera montero j 
-  esp </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>4AuIPRuq</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>EJmuzs93</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>IVonL9jm</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">barrera r 
-  esp </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>nZQG5IgJ</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>MLJrZ3Jt</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>hA5zaJZp</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">maeso f 
-  esp </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Ojpfg5p9</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>nDP2jHyH</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>MNr3HRkC</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">diaz de mera i 
-  esp </t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>WC1tKXIF</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>U3wM1J72</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>ChPK4l66</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ruiz a 
-  esp </t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>IJEltJ2H</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>A7v4ruhp</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>hpMqQeYq</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ortiz m 
-  esp </t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>KWIuYKwG</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>b3KjrVYq</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>4KmdZaBc</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">villanueva j  i 
-  esp </t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>4AuIPRuq</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>bs5KnIiT</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>8CpDVHAM</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">villanueva j  i 
-  esp </t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>0Q3vjDhH</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>bs5KnIiT</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>ng6idLW1</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">villanueva j  i 
-  esp </t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>0Q3vjDhH</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>bs5KnIiT</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>CWcwKOO8</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">garcia v 
-  esp </t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>nZQG5IgJ</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
         <is>
           <t>p2dFnNso</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -765,7 +765,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>ng6idLW1</t>
+          <t>vJDNK0d4</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -773,42 +773,224 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">villanueva j  i 
+          <t xml:space="preserve">garcia v 
   esp </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0Q3vjDhH</t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>bs5KnIiT</t>
+          <t>p2dFnNso</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
+          <t>WhAFMMRi</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AD5WKzFn</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>OQqSjnv9</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>YcAFQVSP</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>IVonL9jm</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrera r 
+  esp </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>hA5zaJZp</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maeso f 
+  esp </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>MNr3HRkC</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diaz de mera i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>ng6idLW1</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villanueva j  i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>bs5KnIiT</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
           <t>CWcwKOO8</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t xml:space="preserve">garcia v 
   esp </t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>nZQG5IgJ</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>p2dFnNso</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,59 +453,49 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hO0nKEm3</t>
+          <t>ITdtTrn2</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">garcia v 
-  esp </t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0Q3vjDhH</t>
+          <t>IilCZTta</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>p2dFnNso</t>
+          <t>fmK213Ku</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>QyafIhIF</t>
+          <t>E1Xs9lu2</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ruiz a 
-  esp </t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>nZQG5IgJ</t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>A7v4ruhp</t>
+          <t>AZ18LjKN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>nDzACNof</t>
+          <t>8KIT2SzJ</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -513,7 +503,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">maeso f 
+          <t xml:space="preserve">sanchez j 
   esp </t>
         </is>
       </c>
@@ -524,14 +514,14 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>nDP2jHyH</t>
+          <t>OjfahOtr</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hnqZAAAk</t>
+          <t>QekfJmLa</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -539,25 +529,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">villanueva j  i 
+          <t xml:space="preserve">lopez m 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
+          <t>fmK213Ku</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>bs5KnIiT</t>
+          <t>KdlyyNgc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ruUIA1G6</t>
+          <t>vJDNK0d4</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -565,25 +555,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">alvendiz l 
+          <t xml:space="preserve">grado c  s 
   esp </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>25GxoIxN</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qkg2vOrk</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>KbKTWiX8</t>
+          <t>WhAFMMRi</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -591,25 +581,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">villanueva j  i 
+          <t xml:space="preserve">ruiz a 
   esp </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>b3KjrVYq</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>bs5KnIiT</t>
+          <t>4AuIPRuq</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Eax2EqHs</t>
+          <t>OQqSjnv9</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -617,25 +607,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera montero j 
+          <t xml:space="preserve">hernandez a 
   esp </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>IJEltJ2H</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>EJmuzs93</t>
+          <t>0Q3vjDhH</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>M3h3GWnS</t>
+          <t>YcAFQVSP</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -643,25 +633,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">diaz de mera i 
+          <t xml:space="preserve">hernandez a 
   esp </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4AuIPRuq</t>
+          <t>EJmuzs93</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>U3wM1J72</t>
+          <t>0Q3vjDhH</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>ITdtTrn2</t>
+          <t>IVonL9jm</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -669,25 +659,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">vega a  c 
+          <t xml:space="preserve">barrera r 
   esp </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>IilCZTta</t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>fmK213Ku</t>
+          <t>MLJrZ3Jt</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>E1Xs9lu2</t>
+          <t>hA5zaJZp</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -695,25 +685,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanchez j 
+          <t xml:space="preserve">maeso f 
   esp </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>25GxoIxN</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AZ18LjKN</t>
+          <t>WC1tKXIF</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8KIT2SzJ</t>
+          <t>MNr3HRkC</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -732,14 +722,14 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>b3KjrVYq</t>
+          <t>02EXFpEP</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>QekfJmLa</t>
+          <t>ChPK4l66</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -747,25 +737,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">lopez m 
+          <t xml:space="preserve">ortiz m 
   esp </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AD5WKzFn</t>
+          <t>IJEltJ2H</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>KdlyyNgc</t>
+          <t>02EXFpEP</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>hpMqQeYq</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -773,7 +763,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">garcia v 
+          <t xml:space="preserve">quintero a 
   esp </t>
         </is>
       </c>
@@ -784,14 +774,14 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>p2dFnNso</t>
+          <t>nDP2jHyH</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
+          <t>4KmdZaBc</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -799,25 +789,25 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera montero j 
+          <t xml:space="preserve">maeso f 
   esp </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>AD5WKzFn</t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>EJmuzs93</t>
+          <t>WC1tKXIF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>OQqSjnv9</t>
+          <t>8CpDVHAM</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -831,19 +821,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>IJEltJ2H</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AZ18LjKN</t>
+          <t>OjfahOtr</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>YcAFQVSP</t>
+          <t>0Y1WIvRG</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -851,25 +841,25 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera montero j 
+          <t xml:space="preserve">sanchez j 
   esp </t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4AuIPRuq</t>
+          <t>EJmuzs93</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>EJmuzs93</t>
+          <t>OjfahOtr</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>IVonL9jm</t>
+          <t>f92vnwe3</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -877,25 +867,25 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">barrera r 
+          <t xml:space="preserve">pulido j 
   esp </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>nZQG5IgJ</t>
+          <t>IilCZTta</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MLJrZ3Jt</t>
+          <t>Ojpfg5p9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hA5zaJZp</t>
+          <t>KhwykQ8L</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -903,25 +893,25 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">maeso f 
+          <t xml:space="preserve">vega a  c 
   esp </t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Ojpfg5p9</t>
+          <t>IJEltJ2H</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>nDP2jHyH</t>
+          <t>fmK213Ku</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MNr3HRkC</t>
+          <t>v1KiOZ2d</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -929,25 +919,25 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">diaz de mera i 
+          <t xml:space="preserve">quintero a 
   esp </t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
+          <t>IJEltJ2H</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>U3wM1J72</t>
+          <t>nDP2jHyH</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>ng6idLW1</t>
+          <t>CQ0ABdJj</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -955,44 +945,356 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">villanueva j  i 
+          <t xml:space="preserve">pulido j 
   esp </t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0Q3vjDhH</t>
+          <t>U3wM1J72</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>bs5KnIiT</t>
+          <t>Ojpfg5p9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
+          <t>0ns5XwtA</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grado c  s 
+  esp </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>OlferefS</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">barrera r 
+  esp </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>SM0npHPF</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>GOO6q4Wr</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>xhKUdf9L</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grado c  s 
+  esp </t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>EJYZzDn2</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lopez m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>tQQLbGv9</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maeso f 
+  esp </t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>vyy1kC1e</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quintero a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>n1v9mjW7</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ortiz m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>h4pRxZHk</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>YN50iYWr</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ortiz m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>ng6idLW1</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
           <t>CWcwKOO8</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">garcia v 
-  esp </t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grado c  s 
+  esp </t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
         <is>
           <t>nZQG5IgJ</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>p2dFnNso</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hO0nKEm3</t>
+          <t>8KIT2SzJ</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -461,25 +461,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">garcia v 
+          <t xml:space="preserve">sanchez j 
   esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0Q3vjDhH</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>p2dFnNso</t>
+          <t>OjfahOtr</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>QyafIhIF</t>
+          <t>QekfJmLa</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -487,25 +487,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ruiz a 
+          <t xml:space="preserve">cuadra g 
   esp </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>nZQG5IgJ</t>
+          <t>fmK213Ku</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>A7v4ruhp</t>
+          <t>AZ18LjKN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>nDzACNof</t>
+          <t>vJDNK0d4</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -513,25 +513,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">maeso f 
+          <t xml:space="preserve">grado c  s 
   esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>25GxoIxN</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>nDP2jHyH</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hnqZAAAk</t>
+          <t>WhAFMMRi</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -539,25 +539,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">villanueva j  i 
+          <t xml:space="preserve">ruiz a 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
+          <t>b3KjrVYq</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>bs5KnIiT</t>
+          <t>4AuIPRuq</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ruUIA1G6</t>
+          <t>OQqSjnv9</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -565,25 +565,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">alvendiz l 
+          <t xml:space="preserve">hernandez a 
   esp </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>MLJrZ3Jt</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Qkg2vOrk</t>
+          <t>0Q3vjDhH</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>KbKTWiX8</t>
+          <t>YcAFQVSP</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -591,25 +591,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">villanueva j  i 
+          <t xml:space="preserve">hernandez a 
   esp </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>EJmuzs93</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>bs5KnIiT</t>
+          <t>0Q3vjDhH</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Eax2EqHs</t>
+          <t>IVonL9jm</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -617,25 +617,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera montero j 
+          <t xml:space="preserve">fuertes p 
   esp </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>IJEltJ2H</t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>EJmuzs93</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>M3h3GWnS</t>
+          <t>hA5zaJZp</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -643,25 +643,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">diaz de mera i 
+          <t xml:space="preserve">maeso f 
   esp </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4AuIPRuq</t>
+          <t>25GxoIxN</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>U3wM1J72</t>
+          <t>WC1tKXIF</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>ITdtTrn2</t>
+          <t>MNr3HRkC</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -669,25 +669,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">vega a  c 
+          <t xml:space="preserve">ortiz m 
   esp </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>IilCZTta</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>fmK213Ku</t>
+          <t>02EXFpEP</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>E1Xs9lu2</t>
+          <t>ChPK4l66</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -695,25 +695,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanchez j 
+          <t xml:space="preserve">ortiz m 
   esp </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>Ii1Om118</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AZ18LjKN</t>
+          <t>02EXFpEP</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8KIT2SzJ</t>
+          <t>hpMqQeYq</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -721,25 +721,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ortiz m 
+          <t xml:space="preserve">quintero a 
   esp </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>Ii1Om118</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>b3KjrVYq</t>
+          <t>nDP2jHyH</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>QekfJmLa</t>
+          <t>4KmdZaBc</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -747,25 +747,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">lopez m 
+          <t xml:space="preserve">maeso f 
   esp </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AD5WKzFn</t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>KdlyyNgc</t>
+          <t>WC1tKXIF</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>8CpDVHAM</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -773,25 +773,25 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">garcia v 
+          <t xml:space="preserve">sanchez j 
   esp </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>IJEltJ2H</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>p2dFnNso</t>
+          <t>OjfahOtr</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
+          <t>0Y1WIvRG</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -799,25 +799,25 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera montero j 
+          <t xml:space="preserve">sanchez j 
   esp </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>AD5WKzFn</t>
+          <t>EJmuzs93</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>EJmuzs93</t>
+          <t>OjfahOtr</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>OQqSjnv9</t>
+          <t>f92vnwe3</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -825,25 +825,25 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanchez j 
+          <t xml:space="preserve">pulido j 
   esp </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>MLJrZ3Jt</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AZ18LjKN</t>
+          <t>Ojpfg5p9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>YcAFQVSP</t>
+          <t>KhwykQ8L</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -851,25 +851,25 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera montero j 
+          <t xml:space="preserve">fuertes p 
   esp </t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4AuIPRuq</t>
+          <t>Ii1Om118</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>EJmuzs93</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>IVonL9jm</t>
+          <t>v1KiOZ2d</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -877,25 +877,25 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">barrera r 
+          <t xml:space="preserve">quintero a 
   esp </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>nZQG5IgJ</t>
+          <t>IJEltJ2H</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>MLJrZ3Jt</t>
+          <t>nDP2jHyH</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hA5zaJZp</t>
+          <t>CQ0ABdJj</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -903,25 +903,25 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">maeso f 
+          <t xml:space="preserve">pulido j 
   esp </t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>Ojpfg5p9</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>nDP2jHyH</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MNr3HRkC</t>
+          <t>0ns5XwtA</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -929,25 +929,25 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">diaz de mera i 
+          <t xml:space="preserve">grado c  s 
   esp </t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
+          <t>fmK213Ku</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>U3wM1J72</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>ng6idLW1</t>
+          <t>OlferefS</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -955,44 +955,304 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">villanueva j  i 
+          <t xml:space="preserve">fuertes p 
   esp </t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0Q3vjDhH</t>
+          <t>b3KjrVYq</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>bs5KnIiT</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
+          <t>SM0npHPF</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cuadra g 
+  esp </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>GOO6q4Wr</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>xhKUdf9L</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grado c  s 
+  esp </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>EJYZzDn2</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cuadra g 
+  esp </t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>tQQLbGv9</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maeso f 
+  esp </t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>vyy1kC1e</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quintero a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>n1v9mjW7</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ortiz m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>h4pRxZHk</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>YN50iYWr</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ortiz m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>ng6idLW1</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
           <t>CWcwKOO8</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">garcia v 
-  esp </t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grado c  s 
+  esp </t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
         <is>
           <t>nZQG5IgJ</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>p2dFnNso</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1204,58 +1204,6 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>ng6idLW1</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sanchez j 
-  esp </t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>EJmuzs93</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>OjfahOtr</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>CWcwKOO8</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">grado c  s 
-  esp </t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>KWIuYKwG</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>nZQG5IgJ</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -448,80 +453,578 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vJDNK0d4</t>
+          <t>IVonL9jm</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>25GxoIxN</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>nZQG5IgJ</t>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>WhAFMMRi</t>
+          <t>hA5zaJZp</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>b3KjrVYq</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4AuIPRuq</t>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>OQqSjnv9</t>
+          <t>MNr3HRkC</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>MLJrZ3Jt</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0Q3vjDhH</t>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>YcAFQVSP</t>
+          <t>ChPK4l66</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Ii1Om118</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>hpMqQeYq</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>4KmdZaBc</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diaz de mera i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>8CpDVHAM</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gil manzano j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>EJmuzs93</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>0Y1WIvRG</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>f92vnwe3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pulido j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>KhwykQ8L</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fuertes p 
+  esp </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Ii1Om118</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>v1KiOZ2d</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quintero a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>CQ0ABdJj</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vega a  c 
+  esp </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>0ns5XwtA</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grado c  s 
+  esp </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>OlferefS</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fuertes p 
+  esp </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>SM0npHPF</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cuadra g 
+  esp </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>GOO6q4Wr</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t>0Q3vjDhH</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>xhKUdf9L</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vega a  c 
+  esp </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>EJYZzDn2</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diaz de mera i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>tQQLbGv9</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maeso f 
+  esp </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vyy1kC1e</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>n1v9mjW7</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ortiz m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>h4pRxZHk</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>YN50iYWr</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ortiz m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>IVonL9jm</t>
+          <t>hpMqQeYq</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -462,19 +462,19 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>WC1tKXIF</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>b3KjrVYq</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hA5zaJZp</t>
+          <t>4KmdZaBc</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -488,14 +488,14 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
+          <t>KdlyyNgc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>MNr3HRkC</t>
+          <t>8CpDVHAM</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -504,19 +504,19 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>4AuIPRuq</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>02EXFpEP</t>
+          <t>EJmuzs93</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>ChPK4l66</t>
+          <t>0Y1WIvRG</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -525,331 +525,306 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ii1Om118</t>
+          <t>OjfahOtr</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>02EXFpEP</t>
+          <t>b3KjrVYq</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hpMqQeYq</t>
+          <t>f92vnwe3</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>KhwykQ8L</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Ii1Om118</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>v1KiOZ2d</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>CQ0ABdJj</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>0ns5XwtA</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>OlferefS</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">garcia v 
+  esp </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>SM0npHPF</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cuadra g 
+  esp </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>GOO6q4Wr</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rojas j  a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>xhKUdf9L</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vega a  c 
+  esp </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>EJYZzDn2</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diaz de mera i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>tQQLbGv9</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bengoetxea r 
+  esp </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>vyy1kC1e</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t xml:space="preserve">munuera montero j 
   esp </t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>WC1tKXIF</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t>b3KjrVYq</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>4KmdZaBc</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">diaz de mera i 
-  esp </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>25GxoIxN</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>KdlyyNgc</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8CpDVHAM</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gil manzano j 
-  esp </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>IJEltJ2H</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>EJmuzs93</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>0Y1WIvRG</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">munuera montero j 
-  esp </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>OjfahOtr</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>b3KjrVYq</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>f92vnwe3</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pulido j 
-  esp </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>MLJrZ3Jt</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Ojpfg5p9</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>KhwykQ8L</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fuertes p 
-  esp </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Ii1Om118</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>UsfeP2jC</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>v1KiOZ2d</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">quintero a 
-  esp </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>IJEltJ2H</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>nDP2jHyH</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>CQ0ABdJj</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vega a  c 
-  esp </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>U3wM1J72</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>KWIuYKwG</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>0ns5XwtA</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">grado c  s 
-  esp </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>fmK213Ku</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>nZQG5IgJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>OlferefS</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fuertes p 
-  esp </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>OjfahOtr</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>UsfeP2jC</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>SM0npHPF</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cuadra g 
-  esp </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>OjfahOtr</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>AZ18LjKN</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>GOO6q4Wr</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hernandez a 
-  esp </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>MLJrZ3Jt</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0Q3vjDhH</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -857,25 +832,25 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">vega a  c 
+          <t xml:space="preserve">ortiz m 
   esp </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>25GxoIxN</t>
+          <t>WC1tKXIF</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>02EXFpEP</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>EJYZzDn2</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -883,25 +858,25 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">diaz de mera i 
+          <t xml:space="preserve">lopez m 
   esp </t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>4AuIPRuq</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>KdlyyNgc</t>
+          <t>IJEltJ2H</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>tQQLbGv9</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -909,122 +884,18 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">maeso f 
+          <t xml:space="preserve">busquets ferrer m 
   esp </t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>vyy1kC1e</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">munuera montero j 
-  esp </t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>25GxoIxN</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>b3KjrVYq</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>n1v9mjW7</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ortiz m 
-  esp </t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>WC1tKXIF</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>02EXFpEP</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>h4pRxZHk</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hernandez a 
-  esp </t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>EJmuzs93</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0Q3vjDhH</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>YN50iYWr</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ortiz m 
-  esp </t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>KWIuYKwG</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>02EXFpEP</t>
+          <t>U3wM1J72</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hpMqQeYq</t>
+          <t>0Y1WIvRG</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -462,7 +462,7 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
+          <t>OjfahOtr</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -474,7 +474,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>4KmdZaBc</t>
+          <t>f92vnwe3</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -483,19 +483,19 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>25GxoIxN</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KdlyyNgc</t>
+          <t>fmK213Ku</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>8CpDVHAM</t>
+          <t>KhwykQ8L</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -504,19 +504,19 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4AuIPRuq</t>
+          <t>AZ18LjKN</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>EJmuzs93</t>
+          <t>IJEltJ2H</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>0Y1WIvRG</t>
+          <t>v1KiOZ2d</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -525,19 +525,19 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>OjfahOtr</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>b3KjrVYq</t>
+          <t>U3wM1J72</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>f92vnwe3</t>
+          <t>CQ0ABdJj</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -546,19 +546,19 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>nZQG5IgJ</t>
+          <t>AZ18LjKN</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>fmK213Ku</t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>KhwykQ8L</t>
+          <t>0ns5XwtA</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -567,82 +567,97 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ii1Om118</t>
+          <t>Ojpfg5p9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>IJEltJ2H</t>
+          <t>MLJrZ3Jt</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>v1KiOZ2d</t>
+          <t>OlferefS</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">garcia v 
+  esp </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>OjfahOtr</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>U3wM1J72</t>
+          <t>MLJrZ3Jt</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>CQ0ABdJj</t>
+          <t>SM0npHPF</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera j 
+  esp </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>U3wM1J72</t>
+          <t>OjfahOtr</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>02EXFpEP</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>0ns5XwtA</t>
+          <t>GOO6q4Wr</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rojas j  a 
+  esp </t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ojpfg5p9</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MLJrZ3Jt</t>
+          <t>0Q3vjDhH</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>OlferefS</t>
+          <t>xhKUdf9L</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -650,25 +665,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">garcia v 
+          <t xml:space="preserve">ruiz a 
   esp </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>OjfahOtr</t>
+          <t>Ojpfg5p9</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>MLJrZ3Jt</t>
+          <t>WC1tKXIF</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>SM0npHPF</t>
+          <t>EJYZzDn2</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -676,25 +691,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">cuadra g 
+          <t xml:space="preserve">ortiz m 
   esp </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>OjfahOtr</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AZ18LjKN</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>GOO6q4Wr</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -702,25 +717,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">rojas j  a 
+          <t xml:space="preserve">bengoetxea r 
   esp </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>nDP2jHyH</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0Q3vjDhH</t>
+          <t>fmK213Ku</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>vyy1kC1e</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -728,25 +743,25 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">vega a  c 
+          <t xml:space="preserve">ortiz m 
   esp </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Ojpfg5p9</t>
+          <t>25GxoIxN</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>EJYZzDn2</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -754,25 +769,25 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">diaz de mera i 
+          <t xml:space="preserve">munuera j 
   esp </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>KdlyyNgc</t>
+          <t>02EXFpEP</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>tQQLbGv9</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -780,25 +795,25 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">bengoetxea r 
+          <t xml:space="preserve">lopez m 
   esp </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>nDP2jHyH</t>
+          <t>4AuIPRuq</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>fmK213Ku</t>
+          <t>IJEltJ2H</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>vyy1kC1e</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -806,94 +821,16 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera montero j 
+          <t xml:space="preserve">busquets ferrer m 
   esp </t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>25GxoIxN</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
-        <is>
-          <t>b3KjrVYq</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>n1v9mjW7</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ortiz m 
-  esp </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>WC1tKXIF</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>02EXFpEP</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>h4pRxZHk</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lopez m 
-  esp </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>4AuIPRuq</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>IJEltJ2H</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>YN50iYWr</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">busquets ferrer m 
-  esp </t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>nZQG5IgJ</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
         <is>
           <t>U3wM1J72</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,15 +436,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>referee</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -453,133 +448,127 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0Y1WIvRG</t>
+          <t>OlferefS</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>OjfahOtr</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>b3KjrVYq</t>
+          <t>Ojpfg5p9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>f92vnwe3</t>
+          <t>SM0npHPF</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>nZQG5IgJ</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>fmK213Ku</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KhwykQ8L</t>
+          <t>GOO6q4Wr</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AZ18LjKN</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>IJEltJ2H</t>
+          <t>OjfahOtr</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>v1KiOZ2d</t>
+          <t>xhKUdf9L</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>U3wM1J72</t>
+          <t>WC1tKXIF</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>CQ0ABdJj</t>
+          <t>EJYZzDn2</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AZ18LjKN</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>KWIuYKwG</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>0ns5XwtA</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ojpfg5p9</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>MLJrZ3Jt</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>OlferefS</t>
+          <t>vyy1kC1e</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -587,25 +576,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">garcia v 
-  esp </t>
+          <t>02EXFpEP</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>OjfahOtr</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>MLJrZ3Jt</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SM0npHPF</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -613,25 +596,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera j 
-  esp </t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>OjfahOtr</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>02EXFpEP</t>
+          <t>25GxoIxN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>GOO6q4Wr</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -639,25 +616,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">rojas j  a 
-  esp </t>
+          <t>4AuIPRuq</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0Q3vjDhH</t>
+          <t>nDP2jHyH</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -665,172 +636,10 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ruiz a 
-  esp </t>
+          <t>fmK213Ku</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
-        <is>
-          <t>Ojpfg5p9</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>WC1tKXIF</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>EJYZzDn2</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ortiz m 
-  esp </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>UDgEKBbq</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>UDgEKBbq</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>tQQLbGv9</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bengoetxea r 
-  esp </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>nDP2jHyH</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>fmK213Ku</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>vyy1kC1e</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ortiz m 
-  esp </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>25GxoIxN</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>UDgEKBbq</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>n1v9mjW7</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">munuera j 
-  esp </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>KWIuYKwG</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>02EXFpEP</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>h4pRxZHk</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lopez m 
-  esp </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>4AuIPRuq</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>IJEltJ2H</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>YN50iYWr</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">busquets ferrer m 
-  esp </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>nZQG5IgJ</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
         <is>
           <t>U3wM1J72</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>OlferefS</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -456,19 +456,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0Q3vjDhH</t>
+          <t>IJEltJ2H</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ojpfg5p9</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SM0npHPF</t>
+          <t>vyy1kC1e</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -476,19 +476,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>EJmuzs93</t>
+          <t>02EXFpEP</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>GOO6q4Wr</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -496,19 +496,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AZ18LjKN</t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>OjfahOtr</t>
+          <t>25GxoIxN</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>xhKUdf9L</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -516,19 +516,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MLJrZ3Jt</t>
+          <t>4AuIPRuq</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
+          <t>nDP2jHyH</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>EJYZzDn2</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -536,110 +536,10 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>EJmuzs93</t>
+          <t>fmK213Ku</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
-        <is>
-          <t>UDgEKBbq</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>tQQLbGv9</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>IJEltJ2H</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>nZQG5IgJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>vyy1kC1e</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>02EXFpEP</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>UDgEKBbq</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>n1v9mjW7</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>KWIuYKwG</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>25GxoIxN</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>h4pRxZHk</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>4AuIPRuq</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>nDP2jHyH</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>YN50iYWr</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>fmK213Ku</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
         <is>
           <t>U3wM1J72</t>
         </is>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -448,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>tQQLbGv9</t>
+          <t>YeqTho8m</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -456,19 +461,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IJEltJ2H</t>
+          <t xml:space="preserve">lopez m 
+  esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>vyy1kC1e</t>
+          <t>08zpk37C</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -476,19 +487,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>02EXFpEP</t>
+          <t xml:space="preserve">gil manzano j 
+  esp </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>n1v9mjW7</t>
+          <t>CjIFsr1e</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -496,19 +513,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t xml:space="preserve">garcia v 
+  esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>25GxoIxN</t>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>h4pRxZHk</t>
+          <t>8EcB5Oig</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -516,19 +539,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4AuIPRuq</t>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>nDP2jHyH</t>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YN50iYWr</t>
+          <t>jckS1tiI</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -536,12 +565,148 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fmK213Ku</t>
+          <t xml:space="preserve">rojas j  a 
+  esp </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>U3wM1J72</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>SfxxiPx0</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diaz de mera i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>na927pNt</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diaz de mera i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>dzUhmsxP</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>SdHeBgOE</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gil manzano j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>fVeJ32M5</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -710,6 +710,422 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>AyPaTn1c</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>8b5vHIeT</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>xjut9IFr</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>IRBb0lXA</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>dYbQEmn4</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>4b2YCRGG</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">garcia v 
+  esp </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>xWrPG9Hi</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>ImLNuMV7</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vega a  c 
+  esp </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>dCNk2A2b</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lopez m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>OAmz0KLU</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>pxdwg6Pp</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diaz de mera i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>QiF6bS1N</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>445r4WXo</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lopez m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>rkN7RQV9</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diaz de mera i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>bwZsTw7E</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>f5SjRHyR</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">garcia v 
+  esp </t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SfxxiPx0</t>
+          <t>AyPaTn1c</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -462,19 +462,19 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>25GxoIxN</t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MLJrZ3Jt</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>na927pNt</t>
+          <t>8b5vHIeT</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -483,19 +483,19 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
+          <t>U3wM1J72</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MLJrZ3Jt</t>
+          <t>4AuIPRuq</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dzUhmsxP</t>
+          <t>xjut9IFr</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -504,61 +504,71 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>nDP2jHyH</t>
+          <t>U3wM1J72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AZ18LjKN</t>
+          <t>EJmuzs93</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SdHeBgOE</t>
+          <t>IRBb0lXA</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">busquets ferrer m 
+  esp </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EJmuzs93</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>KdlyyNgc</t>
+          <t>4AuIPRuq</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fVeJ32M5</t>
+          <t>dYbQEmn4</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera j 
+  esp </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>AyPaTn1c</t>
+          <t>4b2YCRGG</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -566,18 +576,668 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera montero j 
+          <t xml:space="preserve">ortiz m 
   esp </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>xWrPG9Hi</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ruiz a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ImLNuMV7</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pulido j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>dCNk2A2b</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fuertes p 
+  esp </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>OAmz0KLU</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maeso f 
+  esp </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>pxdwg6Pp</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ruiz a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>KWIuYKwG</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>QiF6bS1N</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grado c  s 
+  esp </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>445r4WXo</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bengoetxea r 
+  esp </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>rkN7RQV9</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maeso f 
+  esp </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>bwZsTw7E</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quintero a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>f5SjRHyR</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pulido j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ddsD5q9j</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quintero a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>QDjsB5oT</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">busquets ferrer m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>bqbA3PNE</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bengoetxea r 
+  esp </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>6VWd5zF7</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fuertes p 
+  esp </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>pGrl7dpe</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grado c  s 
+  esp </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>06X4YYrf</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bengoetxea r 
+  esp </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>hMoEUjrJ</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pulido j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>KSw0hfzQ</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fuertes p 
+  esp </t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>YemQuHjK</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grado c  s 
+  esp </t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>4vvdzeEs</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ruiz a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>h0AwIDbD</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ruiz a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>jyEMLeal</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">busquets ferrer m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>4rQsoH7m</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pulido j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>n37VJZT0</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>YJVCWCD6</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ortiz m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SfxxiPx0</t>
+          <t>445r4WXo</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -462,103 +462,123 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>25GxoIxN</t>
+          <t>U3wM1J72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MLJrZ3Jt</t>
+          <t>IJEltJ2H</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>na927pNt</t>
+          <t>rkN7RQV9</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cuadra g 
+  esp </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
+          <t>nDP2jHyH</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MLJrZ3Jt</t>
+          <t>IJEltJ2H</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dzUhmsxP</t>
+          <t>bwZsTw7E</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diaz de mera i 
+  esp </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>nDP2jHyH</t>
+          <t>b3KjrVYq</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AZ18LjKN</t>
+          <t>fmK213Ku</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SdHeBgOE</t>
+          <t>f5SjRHyR</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rojas j  a 
+  esp </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EJmuzs93</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>KdlyyNgc</t>
+          <t>WC1tKXIF</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fVeJ32M5</t>
+          <t>ddsD5q9j</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lopez m 
+  esp </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>b3KjrVYq</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>AZ18LjKN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>AyPaTn1c</t>
+          <t>QDjsB5oT</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -566,18 +586,616 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t xml:space="preserve">vega a  c 
+  esp </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>bqbA3PNE</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">busquets ferrer m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>6VWd5zF7</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pulido j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>pGrl7dpe</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lopez m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>06X4YYrf</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vega a  c 
+  esp </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>hMoEUjrJ</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rojas j  a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>A7eo6U2U</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>KSw0hfzQ</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vega a  c 
+  esp </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>YemQuHjK</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>4vvdzeEs</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">busquets ferrer m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>h0AwIDbD</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>jyEMLeal</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rojas j  a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>4rQsoH7m</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t xml:space="preserve">munuera montero j 
   esp </t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>KWIuYKwG</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>n37VJZT0</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>YJVCWCD6</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diaz de mera i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>QmPfsURO</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>A7eo6U2U</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>0AJjqex0</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vega a  c 
+  esp </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
         <is>
           <t>IJEltJ2H</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>40FWnYcm</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diaz de mera i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>A7eo6U2U</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>KApUeTtI</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>EB22wLQj</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lopez m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>CQIvoCSa</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">busquets ferrer m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>4Ef51XCt</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>hzRnqjcC</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">busquets ferrer m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>YgnMckC5</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pulido j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>CvbDaBsg</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lopez m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>06X4YYrf</t>
+          <t>h0AwIDbD</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -456,19 +456,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>0Q3vjDhH</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hMoEUjrJ</t>
+          <t>jyEMLeal</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -476,19 +476,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>OjfahOtr</t>
+          <t>EJmuzs93</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>nDP2jHyH</t>
+          <t>MLJrZ3Jt</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KSw0hfzQ</t>
+          <t>4rQsoH7m</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -496,19 +496,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>02EXFpEP</t>
+          <t>fmK213Ku</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Ojpfg5p9</t>
+          <t>KdlyyNgc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>YemQuHjK</t>
+          <t>n37VJZT0</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -516,19 +516,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MLJrZ3Jt</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>25GxoIxN</t>
+          <t>nDP2jHyH</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4vvdzeEs</t>
+          <t>YJVCWCD6</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -536,92 +536,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>b3KjrVYq</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>A7eo6U2U</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>h0AwIDbD</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>UDgEKBbq</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0Q3vjDhH</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>jyEMLeal</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>EJmuzs93</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>MLJrZ3Jt</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>4rQsoH7m</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>fmK213Ku</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>KdlyyNgc</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>n37VJZT0</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>UDgEKBbq</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>nDP2jHyH</t>
+          <t>U3wM1J72</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -448,100 +453,288 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>h0AwIDbD</t>
+          <t>QmPfsURO</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>UDgEKBbq</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>jyEMLeal</t>
+          <t>0AJjqex0</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>EJmuzs93</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>MLJrZ3Jt</t>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>4rQsoH7m</t>
+          <t>40FWnYcm</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>fmK213Ku</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>KdlyyNgc</t>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>n37VJZT0</t>
+          <t>KApUeTtI</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>UDgEKBbq</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>nDP2jHyH</t>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YJVCWCD6</t>
+          <t>EB22wLQj</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>CQIvoCSa</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>4Ef51XCt</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>hzRnqjcC</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>YgnMckC5</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>UsfeP2jC</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>U3wM1J72</t>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>CvbDaBsg</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Gz9WD123</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>YNHbsZ6C</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>ll7vCuXF</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>QmPfsURO</t>
+          <t>4Ef51XCt</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -462,19 +462,19 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0Q3vjDhH</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>b3KjrVYq</t>
+          <t>WC1tKXIF</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>0AJjqex0</t>
+          <t>hzRnqjcC</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -483,19 +483,19 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>U3wM1J72</t>
+          <t>4AuIPRuq</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>OjfahOtr</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>40FWnYcm</t>
+          <t>YgnMckC5</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -504,19 +504,19 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4AuIPRuq</t>
+          <t>EJmuzs93</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>OjfahOtr</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>KApUeTtI</t>
+          <t>CvbDaBsg</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -525,145 +525,175 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>KdlyyNgc</t>
+          <t>IJEltJ2H</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>02EXFpEP</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>EB22wLQj</t>
+          <t>Gz9WD123</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fuertes p 
+  esp </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MLJrZ3Jt</t>
+          <t>4AuIPRuq</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ojpfg5p9</t>
+          <t>0Q3vjDhH</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>CQIvoCSa</t>
+          <t>YNHbsZ6C</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maeso f 
+  esp </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>AZ18LjKN</t>
+          <t>EJmuzs93</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>fmK213Ku</t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>4Ef51XCt</t>
+          <t>ll7vCuXF</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>4AuIPRuq</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hzRnqjcC</t>
+          <t>h2NyhKup</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rojas j  a 
+  esp </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4AuIPRuq</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>OjfahOtr</t>
+          <t>b3KjrVYq</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>YgnMckC5</t>
+          <t>8Uo5ctIM</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">busquets ferrer m 
+  esp </t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EJmuzs93</t>
+          <t>fmK213Ku</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>CvbDaBsg</t>
+          <t>0SQqjbAd</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>1</v>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fuertes p 
+  esp </t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>IJEltJ2H</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>nZQG5IgJ</t>
+          <t>0Q3vjDhH</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Gz9WD123</t>
+          <t>65kl1OIc</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -671,25 +701,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera montero j 
+          <t xml:space="preserve">quintero a 
   esp </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4AuIPRuq</t>
+          <t>AZ18LjKN</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>b3KjrVYq</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>YNHbsZ6C</t>
+          <t>f1xuAJ1S</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -697,25 +727,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">hernandez a 
+          <t xml:space="preserve">sanchez j 
   esp </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EJmuzs93</t>
+          <t>KdlyyNgc</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>25GxoIxN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>ll7vCuXF</t>
+          <t>2Xrca2mA</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -723,7 +753,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">hernandez a 
+          <t xml:space="preserve">grado c  s 
   esp </t>
         </is>
       </c>
@@ -734,7 +764,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>WC1tKXIF</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,91 +453,111 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>4Ef51XCt</t>
+          <t>Gz9WD123</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fuertes p 
+  esp </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>nDP2jHyH</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
+          <t>0Q3vjDhH</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hzRnqjcC</t>
+          <t>YNHbsZ6C</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maeso f 
+  esp </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4AuIPRuq</t>
+          <t>02EXFpEP</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>OjfahOtr</t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>YgnMckC5</t>
+          <t>ll7vCuXF</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera j 
+  esp </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EJmuzs93</t>
+          <t>4AuIPRuq</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>U3wM1J72</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>CvbDaBsg</t>
+          <t>h2NyhKup</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diaz de mera i 
+  esp </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>IJEltJ2H</t>
+          <t>02EXFpEP</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>nZQG5IgJ</t>
+          <t>AZ18LjKN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Gz9WD123</t>
+          <t>8Uo5ctIM</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -545,25 +565,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuertes p 
+          <t xml:space="preserve">cuadra g 
   esp </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4AuIPRuq</t>
+          <t>fmK213Ku</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0Q3vjDhH</t>
+          <t>KdlyyNgc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>YNHbsZ6C</t>
+          <t>0SQqjbAd</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -571,25 +591,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">maeso f 
+          <t xml:space="preserve">fuertes p 
   esp </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EJmuzs93</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>0Q3vjDhH</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>ll7vCuXF</t>
+          <t>65kl1OIc</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -597,25 +617,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">hernandez a 
+          <t xml:space="preserve">quintero a 
   esp </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4AuIPRuq</t>
+          <t>IJEltJ2H</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>b3KjrVYq</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>h2NyhKup</t>
+          <t>f1xuAJ1S</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -623,25 +643,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">rojas j  a 
+          <t xml:space="preserve">sanchez j 
   esp </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>b3KjrVYq</t>
+          <t>25GxoIxN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>8Uo5ctIM</t>
+          <t>2Xrca2mA</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -649,25 +669,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">busquets ferrer m 
+          <t xml:space="preserve">munuera j 
   esp </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>fmK213Ku</t>
+          <t>nDP2jHyH</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>nZQG5IgJ</t>
+          <t>U3wM1J72</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>0SQqjbAd</t>
+          <t>QqTA4cPk</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -675,25 +695,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">fuertes p 
+          <t xml:space="preserve">vega a  c 
   esp </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>Ojpfg5p9</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0Q3vjDhH</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>65kl1OIc</t>
+          <t>vymauDyP</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -701,25 +721,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">quintero a 
+          <t xml:space="preserve">munuera j 
   esp </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AZ18LjKN</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>b3KjrVYq</t>
+          <t>U3wM1J72</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>f1xuAJ1S</t>
+          <t>x88gL4RQ</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -727,25 +747,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanchez j 
+          <t xml:space="preserve">cuadra g 
   esp </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>KdlyyNgc</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>25GxoIxN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>2Xrca2mA</t>
+          <t>dhkQFrkl</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -753,18 +773,200 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">grado c  s 
+          <t xml:space="preserve">ortiz m 
   esp </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>8Sp1FEw8</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pulido j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>4zlpJdvq</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ortiz m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>02sgHz9e</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vega a  c 
+  esp </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>naHJ2yf2</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quintero a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>842EOIGL</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diaz de mera i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>jiAoNQdE</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>25GxoIxN</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>WC1tKXIF</t>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>E595Qvn9</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pulido j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -459,12 +459,7 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fuertes p 
-  esp </t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>nDP2jHyH</t>
@@ -485,12 +480,7 @@
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">maeso f 
-  esp </t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>02EXFpEP</t>
@@ -511,12 +501,7 @@
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">munuera j 
-  esp </t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>4AuIPRuq</t>
@@ -537,12 +522,7 @@
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">diaz de mera i 
-  esp </t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>02EXFpEP</t>
@@ -563,12 +543,7 @@
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cuadra g 
-  esp </t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>fmK213Ku</t>
@@ -589,12 +564,7 @@
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">fuertes p 
-  esp </t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>UsfeP2jC</t>
@@ -615,12 +585,7 @@
       <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">quintero a 
-  esp </t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>IJEltJ2H</t>
@@ -641,12 +606,7 @@
       <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sanchez j 
-  esp </t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>nZQG5IgJ</t>
@@ -667,12 +627,7 @@
       <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">munuera j 
-  esp </t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>nDP2jHyH</t>
@@ -693,12 +648,7 @@
       <c r="B11" t="n">
         <v>1</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vega a  c 
-  esp </t>
-        </is>
-      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>Ojpfg5p9</t>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,15 +436,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>referee</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -453,19 +448,18 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Gz9WD123</t>
+          <t>0SQqjbAd</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
-        <is>
-          <t>nDP2jHyH</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
         <is>
           <t>0Q3vjDhH</t>
         </is>
@@ -474,449 +468,80 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>YNHbsZ6C</t>
+          <t>65kl1OIc</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>02EXFpEP</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>KWIuYKwG</t>
+          <t>b3KjrVYq</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ll7vCuXF</t>
+          <t>f1xuAJ1S</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4AuIPRuq</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>U3wM1J72</t>
+          <t>25GxoIxN</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>h2NyhKup</t>
+          <t>2Xrca2mA</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>02EXFpEP</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>AZ18LjKN</t>
+          <t>U3wM1J72</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>8Uo5ctIM</t>
+          <t>QqTA4cPk</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>fmK213Ku</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>KdlyyNgc</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>0SQqjbAd</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>UsfeP2jC</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0Q3vjDhH</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>65kl1OIc</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>IJEltJ2H</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>b3KjrVYq</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>f1xuAJ1S</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>nZQG5IgJ</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>25GxoIxN</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>2Xrca2mA</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>nDP2jHyH</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>U3wM1J72</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>QqTA4cPk</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Ojpfg5p9</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
           <t>UDgEKBbq</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>vymauDyP</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">munuera j 
-  esp </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>UsfeP2jC</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>U3wM1J72</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>x88gL4RQ</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cuadra g 
-  esp </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>MLJrZ3Jt</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>KdlyyNgc</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>dhkQFrkl</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ortiz m 
-  esp </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>MLJrZ3Jt</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>OjfahOtr</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>8Sp1FEw8</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pulido j 
-  esp </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>fmK213Ku</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>EJmuzs93</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>4zlpJdvq</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ortiz m 
-  esp </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>nZQG5IgJ</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>OjfahOtr</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>02sgHz9e</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vega a  c 
-  esp </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Ojpfg5p9</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>UDgEKBbq</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>naHJ2yf2</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">quintero a 
-  esp </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>4AuIPRuq</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>b3KjrVYq</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>842EOIGL</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">diaz de mera i 
-  esp </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>WC1tKXIF</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>AZ18LjKN</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>jiAoNQdE</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sanchez j 
-  esp </t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>IJEltJ2H</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>25GxoIxN</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>E595Qvn9</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pulido j 
-  esp </t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>UsfeP2jC</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>EJmuzs93</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -448,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0SQqjbAd</t>
+          <t>vymauDyP</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -456,19 +461,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t xml:space="preserve">bengoetxea r 
+  esp </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0Q3vjDhH</t>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>65kl1OIc</t>
+          <t>x88gL4RQ</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -476,19 +487,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>IJEltJ2H</t>
+          <t xml:space="preserve">garcia v 
+  esp </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>b3KjrVYq</t>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>f1xuAJ1S</t>
+          <t>dhkQFrkl</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -496,19 +513,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nZQG5IgJ</t>
+          <t xml:space="preserve">lopez m 
+  esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>25GxoIxN</t>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2Xrca2mA</t>
+          <t>8Sp1FEw8</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -516,19 +539,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nDP2jHyH</t>
+          <t xml:space="preserve">grado c  s 
+  esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>U3wM1J72</t>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>QqTA4cPk</t>
+          <t>4zlpJdvq</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -536,12 +565,408 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t xml:space="preserve">bengoetxea r 
+  esp </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>02sgHz9e</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>naHJ2yf2</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gil manzano j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>tI57YghG</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>842EOIGL</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>Ojpfg5p9</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>jiAoNQdE</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ruiz a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>E595Qvn9</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">busquets ferrer m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>02cHDDPH</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rojas j  a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>4z48FZf5</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lopez m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>dA00HeQh</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>YFePBifU</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rojas j  a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>zHmSVfun</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hernandez a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>QXtsC0lD</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gil manzano j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>tI57YghG</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>UaS8aGMt</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">busquets ferrer m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>rsizUY9b</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">grado c  s 
+  esp </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>U5mYDMJ0</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ruiz a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>zeCiJHet</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">garcia v 
+  esp </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,15 +436,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>referee</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -461,16 +456,10 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bengoetxea r 
-  esp </t>
+          <t>EJmuzs93</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
-        <is>
-          <t>EJmuzs93</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
         <is>
           <t>WC1tKXIF</t>
         </is>
@@ -487,16 +476,10 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">garcia v 
-  esp </t>
+          <t>nDP2jHyH</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
-        <is>
-          <t>nDP2jHyH</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
         <is>
           <t>4AuIPRuq</t>
         </is>
@@ -513,16 +496,10 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">lopez m 
-  esp </t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
-        <is>
-          <t>KWIuYKwG</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
         <is>
           <t>MLJrZ3Jt</t>
         </is>
@@ -539,16 +516,10 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">grado c  s 
-  esp </t>
+          <t>b3KjrVYq</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
-        <is>
-          <t>b3KjrVYq</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
         <is>
           <t>IJEltJ2H</t>
         </is>
@@ -565,16 +536,10 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">bengoetxea r 
-  esp </t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
-        <is>
-          <t>UDgEKBbq</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
         <is>
           <t>WC1tKXIF</t>
         </is>
@@ -591,16 +556,10 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">hernandez a 
-  esp </t>
+          <t>AZ18LjKN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
-        <is>
-          <t>AZ18LjKN</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
         <is>
           <t>nZQG5IgJ</t>
         </is>
@@ -617,16 +576,10 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gil manzano j 
-  esp </t>
+          <t>KdlyyNgc</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
-        <is>
-          <t>KdlyyNgc</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
         <is>
           <t>tI57YghG</t>
         </is>
@@ -643,16 +596,10 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera montero j 
-  esp </t>
+          <t>25GxoIxN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
-        <is>
-          <t>25GxoIxN</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
         <is>
           <t>Ojpfg5p9</t>
         </is>
@@ -669,16 +616,10 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">ruiz a 
-  esp </t>
+          <t>02EXFpEP</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
-        <is>
-          <t>02EXFpEP</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
         <is>
           <t>U3wM1J72</t>
         </is>
@@ -695,278 +636,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">busquets ferrer m 
-  esp </t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
           <t>UsfeP2jC</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>02cHDDPH</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rojas j  a 
-  esp </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>nDP2jHyH</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0Q3vjDhH</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>4z48FZf5</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lopez m 
-  esp </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>25GxoIxN</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>MLJrZ3Jt</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>dA00HeQh</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">munuera montero j 
-  esp </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>02EXFpEP</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Ojpfg5p9</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>YFePBifU</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rojas j  a 
-  esp </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>KdlyyNgc</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0Q3vjDhH</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>zHmSVfun</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hernandez a 
-  esp </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>b3KjrVYq</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>nZQG5IgJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>QXtsC0lD</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gil manzano j 
-  esp </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>AZ18LjKN</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>tI57YghG</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>UaS8aGMt</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">busquets ferrer m 
-  esp </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>OjfahOtr</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>UsfeP2jC</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>rsizUY9b</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">grado c  s 
-  esp </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>OjfahOtr</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>IJEltJ2H</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>U5mYDMJ0</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ruiz a 
-  esp </t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>EJmuzs93</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>U3wM1J72</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>zeCiJHet</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">garcia v 
-  esp </t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>UDgEKBbq</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>4AuIPRuq</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -448,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vymauDyP</t>
+          <t>02cHDDPH</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -456,19 +461,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t xml:space="preserve">munuera j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>EJmuzs93</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>WC1tKXIF</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>x88gL4RQ</t>
+          <t>4z48FZf5</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -476,19 +487,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nDP2jHyH</t>
+          <t xml:space="preserve">maeso f 
+  esp </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4AuIPRuq</t>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dhkQFrkl</t>
+          <t>dA00HeQh</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -496,19 +513,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t xml:space="preserve">lopez m 
+  esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MLJrZ3Jt</t>
+          <t>tI57YghG</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8Sp1FEw8</t>
+          <t>YFePBifU</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -516,19 +539,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>b3KjrVYq</t>
+          <t xml:space="preserve">vega a  c 
+  esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>IJEltJ2H</t>
+          <t>naiTF0T9</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4zlpJdvq</t>
+          <t>zHmSVfun</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -536,19 +565,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t xml:space="preserve">sanchez j 
+  esp </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>02sgHz9e</t>
+          <t>QXtsC0lD</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -556,19 +591,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AZ18LjKN</t>
+          <t xml:space="preserve">quintero a 
+  esp </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>nZQG5IgJ</t>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>naHJ2yf2</t>
+          <t>UaS8aGMt</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -576,19 +617,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>KdlyyNgc</t>
+          <t xml:space="preserve">ortiz m 
+  esp </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>tI57YghG</t>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>842EOIGL</t>
+          <t>rsizUY9b</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -596,19 +643,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t xml:space="preserve">pulido j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>25GxoIxN</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Ojpfg5p9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>jiAoNQdE</t>
+          <t>U5mYDMJ0</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -616,19 +669,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>02EXFpEP</t>
+          <t xml:space="preserve">gil manzano j 
+  esp </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>U3wM1J72</t>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>E595Qvn9</t>
+          <t>zeCiJHet</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -636,12 +695,278 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t xml:space="preserve">cuadra g 
+  esp </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>rPc4X7Gj</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quintero a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>nucZxUhT</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pulido j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>bXuieB8c</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vega a  c 
+  esp </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>naiTF0T9</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>jFGHcfig</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cuadra g 
+  esp </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>CMriQj9N</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">quintero a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>4duqSCvB</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lopez m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Ia5ItCg4</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gil manzano j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>KWIuYKwG</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>UsfeP2jC</t>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>UwPNKUWp</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ortiz m 
+  esp </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>MXB9rYOi</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>naiTF0T9</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>QP8QvjOG</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +531,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>YFePBifU</t>
+          <t>QXtsC0lD</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -539,25 +539,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">vega a  c 
+          <t xml:space="preserve">quintero a 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>naiTF0T9</t>
+          <t>U3wM1J72</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>nDP2jHyH</t>
+          <t>02EXFpEP</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>zHmSVfun</t>
+          <t>UaS8aGMt</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -565,25 +565,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">sanchez j 
+          <t xml:space="preserve">ortiz m 
   esp </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4AuIPRuq</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>OjfahOtr</t>
+          <t>WC1tKXIF</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>QXtsC0lD</t>
+          <t>rsizUY9b</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -591,25 +591,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">quintero a 
+          <t xml:space="preserve">pulido j 
   esp </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>U3wM1J72</t>
+          <t>UsfeP2jC</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>02EXFpEP</t>
+          <t>25GxoIxN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>UaS8aGMt</t>
+          <t>U5mYDMJ0</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -617,25 +617,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ortiz m 
+          <t xml:space="preserve">gil manzano j 
   esp </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>nZQG5IgJ</t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
+          <t>AZ18LjKN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>rsizUY9b</t>
+          <t>zeCiJHet</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -643,330 +643,18 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">pulido j 
+          <t xml:space="preserve">cuadra g 
   esp </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>Ojpfg5p9</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>25GxoIxN</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>U5mYDMJ0</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gil manzano j 
-  esp </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>KWIuYKwG</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AZ18LjKN</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>zeCiJHet</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cuadra g 
-  esp </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Ojpfg5p9</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
           <t>b3KjrVYq</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>rPc4X7Gj</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">quintero a 
-  esp </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>0Q3vjDhH</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>02EXFpEP</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>nucZxUhT</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pulido j 
-  esp </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>nZQG5IgJ</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>25GxoIxN</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>bXuieB8c</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vega a  c 
-  esp </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>naiTF0T9</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>nDP2jHyH</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>jFGHcfig</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cuadra g 
-  esp </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>UsfeP2jC</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>b3KjrVYq</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>CMriQj9N</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">quintero a 
-  esp </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>4AuIPRuq</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>02EXFpEP</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>4duqSCvB</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lopez m 
-  esp </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>U3wM1J72</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>UDgEKBbq</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Ia5ItCg4</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gil manzano j 
-  esp </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>KWIuYKwG</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>AZ18LjKN</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>UwPNKUWp</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ortiz m 
-  esp </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Ojpfg5p9</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>WC1tKXIF</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>MXB9rYOi</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">munuera j 
-  esp </t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>naiTF0T9</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>EJmuzs93</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>QP8QvjOG</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">sanchez j 
-  esp </t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>IJEltJ2H</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>OjfahOtr</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>02cHDDPH</t>
+          <t>rPc4X7Gj</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -461,7 +461,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">munuera j 
+          <t xml:space="preserve">bengoetxea r 
   esp </t>
         </is>
       </c>
@@ -472,14 +472,14 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>EJmuzs93</t>
+          <t>tI57YghG</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>4z48FZf5</t>
+          <t>nucZxUhT</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -487,25 +487,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">maeso f 
+          <t xml:space="preserve">garcia v 
   esp </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>IJEltJ2H</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>KdlyyNgc</t>
+          <t>MLJrZ3Jt</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dA00HeQh</t>
+          <t>bXuieB8c</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -513,25 +513,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">lopez m 
+          <t xml:space="preserve">fuertes p 
   esp </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>tI57YghG</t>
+          <t>naiTF0T9</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>QXtsC0lD</t>
+          <t>jFGHcfig</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -539,25 +539,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">quintero a 
+          <t xml:space="preserve">cuadra g 
   esp </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>U3wM1J72</t>
+          <t>OjfahOtr</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>02EXFpEP</t>
+          <t>b3KjrVYq</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>UaS8aGMt</t>
+          <t>UwPNKUWp</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -565,25 +565,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ortiz m 
+          <t xml:space="preserve">ruiz a 
   esp </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>nZQG5IgJ</t>
+          <t>02EXFpEP</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
+          <t>IJEltJ2H</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>rsizUY9b</t>
+          <t>4duqSCvB</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -591,25 +591,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">pulido j 
+          <t xml:space="preserve">gil manzano j 
   esp </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>EJmuzs93</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>25GxoIxN</t>
+          <t>4AuIPRuq</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>U5mYDMJ0</t>
+          <t>Ia5ItCg4</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -617,25 +617,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">gil manzano j 
+          <t xml:space="preserve">bengoetxea r 
   esp </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>nDP2jHyH</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AZ18LjKN</t>
+          <t>tI57YghG</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>zeCiJHet</t>
+          <t>CMriQj9N</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -643,18 +643,70 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">cuadra g 
+          <t xml:space="preserve">busquets ferrer m 
   esp </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>Ojpfg5p9</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>b3KjrVYq</t>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>MXB9rYOi</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rojas j  a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>YaDNxIRF</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>QP8QvjOG</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/spain/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,12 +459,7 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bengoetxea r 
-  esp </t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>0Q3vjDhH</t>
@@ -485,228 +480,292 @@
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>bXuieB8c</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>naiTF0T9</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>UwPNKUWp</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>4duqSCvB</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Ia5ItCg4</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>tI57YghG</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>CMriQj9N</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>MXB9rYOi</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>YaDNxIRF</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>QP8QvjOG</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>SCX7iT7M</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve">garcia v 
   esp </t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>nZQG5IgJ</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>MLJrZ3Jt</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>bXuieB8c</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>C2KEmK6l</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rojas j  a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>vVwOqx6D</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">fuertes p 
   esp </t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>naiTF0T9</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>KWIuYKwG</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>jFGHcfig</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cuadra g 
-  esp </t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>OjfahOtr</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>b3KjrVYq</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>UwPNKUWp</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ruiz a 
-  esp </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>02EXFpEP</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>IJEltJ2H</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>4duqSCvB</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gil manzano j 
-  esp </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>EJmuzs93</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>4AuIPRuq</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Ia5ItCg4</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bengoetxea r 
-  esp </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>nDP2jHyH</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>tI57YghG</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>CMriQj9N</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">busquets ferrer m 
-  esp </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>UDgEKBbq</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Ojpfg5p9</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>MXB9rYOi</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rojas j  a 
-  esp </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>YaDNxIRF</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>U3wM1J72</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>QP8QvjOG</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>buKPeYL5</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t xml:space="preserve">munuera montero j 
   esp </t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>WC1tKXIF</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>UsfeP2jC</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>IsCnpo0d</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fuertes p 
+  esp </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
         </is>
       </c>
     </row>
